--- a/Result/profitability/5274.xlsx
+++ b/Result/profitability/5274.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>3.27</v>
       </c>
       <c r="M2" t="n">
-        <v>23.60625</v>
+        <v>26.7275</v>
       </c>
       <c r="N2" t="n">
-        <v>65.74250000000001</v>
+        <v>66.70750000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>2.68</v>
       </c>
       <c r="M3" t="n">
-        <v>21.52875</v>
+        <v>23.94375</v>
       </c>
       <c r="N3" t="n">
-        <v>64.80875</v>
+        <v>65.6275</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -8431,6 +8431,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>3871</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2788</v>
+      </c>
+      <c r="F64" t="n">
+        <v>72</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2086</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>53.88%</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>180</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2265</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1841</v>
+      </c>
+      <c r="L64" t="n">
+        <v>44.27</v>
+      </c>
+      <c r="M64" t="n">
+        <v>28.73125</v>
+      </c>
+      <c r="N64" t="n">
+        <v>67.84125</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>6.860000000000007</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0.1833734295642877</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>2.819999999999993</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.0407632263660016</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.658858858858859</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>4.120000000000005</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.06069534472598703</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
